--- a/results/ai_run/682_z23/5_quantification/682_z23_quantification.xlsx
+++ b/results/ai_run/682_z23/5_quantification/682_z23_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14.0909</v>
+        <v>10.3636</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>4.4374</v>
+        <v>3.2641</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.3641</v>
+        <v>4.6662</v>
       </c>
       <c r="D25" t="n">
-        <v>5.9626</v>
+        <v>4.6282</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4525</v>
+        <v>1.0772</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -2592,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>160</v>
@@ -2631,7 +2631,7 @@
         <v>0.04418856</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.6079</v>
+        <v>3.8039</v>
       </c>
       <c r="Z2" t="n">
         <v>145</v>
@@ -2696,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
         <v>77</v>
@@ -2735,7 +2735,7 @@
         <v>0.02901379</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.5165</v>
+        <v>3.011</v>
       </c>
       <c r="Z3" t="n">
         <v>70</v>
@@ -2800,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -2839,7 +2839,7 @@
         <v>0.03982621</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.5521</v>
+        <v>3.6416</v>
       </c>
       <c r="Z4" t="n">
         <v>314</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M6" t="n">
         <v>537</v>
@@ -3053,7 +3053,7 @@
         <v>0.03975678</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.9626</v>
+        <v>4.7701</v>
       </c>
       <c r="Z6" t="n">
         <v>508</v>
@@ -3121,7 +3121,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
         <v>421</v>
@@ -3160,7 +3160,7 @@
         <v>0.05082111</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.7836</v>
+        <v>2.9898</v>
       </c>
       <c r="Z7" t="n">
         <v>399</v>
@@ -3228,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M8" t="n">
         <v>465</v>
@@ -3267,7 +3267,7 @@
         <v>0.04524846</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.1596</v>
+        <v>5.3383</v>
       </c>
       <c r="Z8" t="n">
         <v>439</v>
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
         <v>460</v>
@@ -3374,7 +3374,7 @@
         <v>0.05582455</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.7416</v>
+        <v>5.9551</v>
       </c>
       <c r="Z9" t="n">
         <v>448</v>
@@ -3442,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
         <v>351</v>
@@ -3481,7 +3481,7 @@
         <v>0.04215808</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.5954</v>
+        <v>3.5349</v>
       </c>
       <c r="Z10" t="n">
         <v>259</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
         <v>546</v>
@@ -3588,7 +3588,7 @@
         <v>0.05559629</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.693</v>
+        <v>3.7954</v>
       </c>
       <c r="Z11" t="n">
         <v>499</v>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M12" t="n">
         <v>311</v>
@@ -3695,7 +3695,7 @@
         <v>0.03558016</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.4494</v>
+        <v>4.0112</v>
       </c>
       <c r="Z12" t="n">
         <v>267</v>
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M13" t="n">
         <v>442</v>
@@ -3802,7 +3802,7 @@
         <v>0.04556312</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.5646</v>
+        <v>6.6614</v>
       </c>
       <c r="Z13" t="n">
         <v>384</v>
@@ -3870,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
         <v>267</v>
@@ -3909,7 +3909,7 @@
         <v>0.03655715</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.3815</v>
+        <v>4.3052</v>
       </c>
       <c r="Z14" t="n">
         <v>257</v>
@@ -3977,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
         <v>323</v>
@@ -4016,7 +4016,7 @@
         <v>0.03331319</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.485099999999999</v>
+        <v>4.6282</v>
       </c>
       <c r="Z15" t="n">
         <v>296</v>
